--- a/天融信vsPA功能对比.xlsx
+++ b/天融信vsPA功能对比.xlsx
@@ -6673,7 +6673,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J28"/>
+  <dimension ref="A1:J31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -6843,7 +6843,7 @@
       </c>
       <c r="J5" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>_sources/web/topsec/topsec-topngfw-product.html（254KB）</t>
         </is>
       </c>
     </row>
@@ -6863,12 +6863,12 @@
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>L1 规格/白皮书</t>
+          <t>L1 产品彩页（规格）</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>待核对</t>
+          <t>NGTOS 平台（2页彩页）</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
@@ -6893,7 +6893,7 @@
       </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
-          <t>待下载归档</t>
+          <t>_sources/docs/topsec_ngfw_product_doc.pdf（26.7MB）</t>
         </is>
       </c>
     </row>
@@ -7001,141 +7001,501 @@
       <c r="A9" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="B9" s="5" t="n"/>
-      <c r="C9" s="5" t="n"/>
-      <c r="D9" s="5" t="n"/>
-      <c r="E9" s="5" t="n"/>
-      <c r="F9" s="5" t="n"/>
-      <c r="G9" s="5" t="n"/>
-      <c r="H9" s="5" t="n"/>
-      <c r="I9" s="5" t="n"/>
-      <c r="J9" s="5" t="n"/>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>PAN-OS 12.1 官方文档门户（英文，特性索引）</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>Palo Alto</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>L2 手册/文档门户</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>12.1</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>持续更新</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>https://docs.paloaltonetworks.com/pan-os</t>
+        </is>
+      </c>
+      <c r="H9" s="5" t="inlineStr">
+        <is>
+          <t>全大类</t>
+        </is>
+      </c>
+      <c r="I9" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="J9" s="5" t="inlineStr">
+        <is>
+          <t>_sources/web/pa/panos-12-1-new-features.html（659KB，新特性页快照；其余按功能点逐页取证）</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="n">
+      <c r="A10" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="B10" s="4" t="n"/>
-      <c r="C10" s="4" t="n"/>
-      <c r="D10" s="4" t="n"/>
-      <c r="E10" s="4" t="n"/>
-      <c r="F10" s="4" t="n"/>
-      <c r="G10" s="4" t="n"/>
-      <c r="H10" s="4" t="n"/>
-      <c r="I10" s="4" t="n"/>
-      <c r="J10" s="4" t="n"/>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>PAN-OS 管理员指南（简体中文版 PDF）</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>Palo Alto</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>L2 手册</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>11.0（中文版；11.1+ 在线版）</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="inlineStr">
+        <is>
+          <t>https://docs.paloaltonetworks.com/content/dam/techdocs/zh_CN/pdf/pan-os/11-0/pan-os-admin-11-0-zh-cn.pdf；中文索引 docs.paloaltonetworks.com/translated/zh-cn</t>
+        </is>
+      </c>
+      <c r="H10" s="5" t="inlineStr">
+        <is>
+          <t>全大类</t>
+        </is>
+      </c>
+      <c r="I10" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="J10" s="5" t="inlineStr">
+        <is>
+          <t>_sources/docs/pa/pan-os-admin-11-0-zh-cn.pdf（3.4MB）</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="B11" s="5" t="n"/>
-      <c r="C11" s="5" t="n"/>
-      <c r="D11" s="5" t="n"/>
-      <c r="E11" s="5" t="n"/>
-      <c r="F11" s="5" t="n"/>
-      <c r="G11" s="5" t="n"/>
-      <c r="H11" s="5" t="n"/>
-      <c r="I11" s="5" t="n"/>
-      <c r="J11" s="5" t="n"/>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>PA NGFW 硬件产品页（产品线全集 PA-400R~7500）</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>Palo Alto</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>L1 产品规格</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>在售全集</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-15 检索</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>https://www.paloaltonetworks.com/network-security/next-generation-firewall-hardware</t>
+        </is>
+      </c>
+      <c r="H11" s="5" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="I11" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="J11" s="5" t="inlineStr">
+        <is>
+          <t>_sources/web/pa/pa-ngfw-hardware.html（1.0MB）</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="n">
+      <c r="A12" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="B12" s="4" t="n"/>
-      <c r="C12" s="4" t="n"/>
-      <c r="D12" s="4" t="n"/>
-      <c r="E12" s="4" t="n"/>
-      <c r="F12" s="4" t="n"/>
-      <c r="G12" s="4" t="n"/>
-      <c r="H12" s="4" t="n"/>
-      <c r="I12" s="4" t="n"/>
-      <c r="J12" s="4" t="n"/>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>Single-Pass Parallel Processing 架构白皮书（入口页）</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>Palo Alto</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>L1 原理</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="inlineStr">
+        <is>
+          <t>https://www.paloaltonetworks.com/resources/whitepapers/single-pass-parallel-processing-architecture</t>
+        </is>
+      </c>
+      <c r="H12" s="5" t="inlineStr">
+        <is>
+          <t>A/C/F</t>
+        </is>
+      </c>
+      <c r="I12" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="J12" s="5" t="inlineStr">
+        <is>
+          <t>P3 需引用时再取全文</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="B13" s="5" t="n"/>
-      <c r="C13" s="5" t="n"/>
-      <c r="D13" s="5" t="n"/>
-      <c r="E13" s="5" t="n"/>
-      <c r="F13" s="5" t="n"/>
-      <c r="G13" s="5" t="n"/>
-      <c r="H13" s="5" t="n"/>
-      <c r="I13" s="5" t="n"/>
-      <c r="J13" s="5" t="n"/>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>PA Certifications 官方页（CC/FIPS 汇总）</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>Palo Alto</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>L3 合规</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-15 检索</t>
+        </is>
+      </c>
+      <c r="G13" s="5" t="inlineStr">
+        <is>
+          <t>https://docs.paloaltonetworks.com/ngfw/administration/certifications</t>
+        </is>
+      </c>
+      <c r="H13" s="5" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="I13" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="J13" s="5" t="inlineStr">
+        <is>
+          <t>_sources/web/pa/panos-certifications.html（286KB）</t>
+        </is>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="n">
+      <c r="A14" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="B14" s="4" t="n"/>
-      <c r="C14" s="4" t="n"/>
-      <c r="D14" s="4" t="n"/>
-      <c r="E14" s="4" t="n"/>
-      <c r="F14" s="4" t="n"/>
-      <c r="G14" s="4" t="n"/>
-      <c r="H14" s="4" t="n"/>
-      <c r="I14" s="4" t="n"/>
-      <c r="J14" s="4" t="n"/>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>Common Criteria Validation Report（NDcPP v3.0e + IPS/ST/VPN PP）</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>第三方权威（Leidos）</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>L3 合规</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>PP-Configuration v2.0（2024-04-25）</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="5" t="inlineStr">
+        <is>
+          <t>https://www.commoncriteriaportal.org/files/epfiles/st_vid11482-vr.pdf（覆盖 PA-400~7000 及 VM 系列）</t>
+        </is>
+      </c>
+      <c r="H14" s="5" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="I14" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="J14" s="5" t="inlineStr">
+        <is>
+          <t>_sources/docs/pa/cc-st_vid11482-vr.pdf（414KB）</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="n">
         <v>12</v>
       </c>
-      <c r="B15" s="5" t="n"/>
-      <c r="C15" s="5" t="n"/>
-      <c r="D15" s="5" t="n"/>
-      <c r="E15" s="5" t="n"/>
-      <c r="F15" s="5" t="n"/>
-      <c r="G15" s="5" t="n"/>
-      <c r="H15" s="5" t="n"/>
-      <c r="I15" s="5" t="n"/>
-      <c r="J15" s="5" t="n"/>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>FIPS 140-3 Level 2 证书（PAN-OS 11.1/11.2 @ PA-400~7500）</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>第三方权威（NIST CMVP）</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>L3 合规</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>FIPS 140-3 L2</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-10 验证（sunset 2031-09-06）</t>
+        </is>
+      </c>
+      <c r="G15" s="5" t="inlineStr">
+        <is>
+          <t>https://sec-certs.org/fips/2e64f1bab2a90810/</t>
+        </is>
+      </c>
+      <c r="H15" s="5" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="I15" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="J15" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="n">
+      <c r="A16" s="5" t="n">
         <v>13</v>
       </c>
-      <c r="B16" s="4" t="n"/>
-      <c r="C16" s="4" t="n"/>
-      <c r="D16" s="4" t="n"/>
-      <c r="E16" s="4" t="n"/>
-      <c r="F16" s="4" t="n"/>
-      <c r="G16" s="4" t="n"/>
-      <c r="H16" s="4" t="n"/>
-      <c r="I16" s="4" t="n"/>
-      <c r="J16" s="4" t="n"/>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>天融信《网络安全专用产品安全检测证书》新闻（网专检测，三类防火墙）</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>天融信</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>L3 合规</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>第一批证书（万兆/千兆/百兆全覆盖）</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G16" s="5" t="inlineStr">
+        <is>
+          <t>https://www.topsec.com.cn/newsx/4441.html</t>
+        </is>
+      </c>
+      <c r="H16" s="5" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="I16" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="J16" s="5" t="inlineStr">
+        <is>
+          <t>_sources/web/topsec/topsec-news-4441-cert.html（234KB）</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="n">
         <v>14</v>
       </c>
-      <c r="B17" s="5" t="n"/>
-      <c r="C17" s="5" t="n"/>
-      <c r="D17" s="5" t="n"/>
-      <c r="E17" s="5" t="n"/>
-      <c r="F17" s="5" t="n"/>
-      <c r="G17" s="5" t="n"/>
-      <c r="H17" s="5" t="n"/>
-      <c r="I17" s="5" t="n"/>
-      <c r="J17" s="5" t="n"/>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>天融信 IPv6 Ready Logo / 互联互通检测证书（新闻页）</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>天融信</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>L3 合规</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G17" s="5" t="inlineStr">
+        <is>
+          <t>https://www.topsec.com.cn/newsx/5604（IPv6 Ready）；/newsx/5437（首批互联互通）</t>
+        </is>
+      </c>
+      <c r="H17" s="5" t="inlineStr">
+        <is>
+          <t>A/H</t>
+        </is>
+      </c>
+      <c r="I17" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="J17" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="B18" s="4" t="n"/>
-      <c r="C18" s="4" t="n"/>
-      <c r="D18" s="4" t="n"/>
-      <c r="E18" s="4" t="n"/>
-      <c r="F18" s="4" t="n"/>
-      <c r="G18" s="4" t="n"/>
-      <c r="H18" s="4" t="n"/>
-      <c r="I18" s="4" t="n"/>
-      <c r="J18" s="4" t="n"/>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>PA-3400 Series Datasheet（PA-3410/3420/3430/3440）</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>Palo Alto</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>L1 Datasheet</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>PA-3400 系列</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="G18" s="4" t="inlineStr">
+        <is>
+          <t>https://www.paloaltonetworks.com/resources/datasheets/pa-3400-series</t>
+        </is>
+      </c>
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t>G/A/C</t>
+        </is>
+      </c>
+      <c r="I18" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="J18" s="4" t="inlineStr">
+        <is>
+          <t>_sources/docs/pa/pa-3400-series-datasheet.pdf（431KB）</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="n">
@@ -7277,6 +7637,9 @@
       <c r="I28" s="4" t="n"/>
       <c r="J28" s="4" t="n"/>
     </row>
+    <row r="29"/>
+    <row r="30"/>
+    <row r="31"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:J1"/>

--- a/天融信vsPA功能对比.xlsx
+++ b/天融信vsPA功能对比.xlsx
@@ -333,7 +333,151 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing_wm1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:absoluteAnchor>
+    <xdr:pos x="6800000" y="6400000"/>
+    <xdr:ext cx="2200000" cy="350000"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1" name="Watermark"/>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="0">
+          <a:off x="0" y="0"/>
+          <a:ext cx="2200000" cy="350000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" rtlCol="0" anchor="b" lIns="0" tIns="0" rIns="0" bIns="0"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="r"/>
+          <a:r>
+            <a:rPr lang="zh-CN" sz="1600" dirty="0">
+              <a:solidFill>
+                <a:srgbClr val="808080">
+                  <a:alpha val="19999"/>
+                </a:srgbClr>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="SimSun"/>
+            </a:rPr>
+            <a:t>AI 生成</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/drawings/drawing_wm2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:absoluteAnchor>
+    <xdr:pos x="6800000" y="6400000"/>
+    <xdr:ext cx="2200000" cy="350000"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1" name="Watermark"/>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="0">
+          <a:off x="0" y="0"/>
+          <a:ext cx="2200000" cy="350000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" rtlCol="0" anchor="b" lIns="0" tIns="0" rIns="0" bIns="0"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="r"/>
+          <a:r>
+            <a:rPr lang="zh-CN" sz="1600" dirty="0">
+              <a:solidFill>
+                <a:srgbClr val="808080">
+                  <a:alpha val="19999"/>
+                </a:srgbClr>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="SimSun"/>
+            </a:rPr>
+            <a:t>AI 生成</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing_wm2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:absoluteAnchor>
+    <xdr:pos x="6800000" y="6400000"/>
+    <xdr:ext cx="2200000" cy="350000"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1" name="Watermark"/>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="0">
+          <a:off x="0" y="0"/>
+          <a:ext cx="2200000" cy="350000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" rtlCol="0" anchor="b" lIns="0" tIns="0" rIns="0" bIns="0"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="r"/>
+          <a:r>
+            <a:rPr lang="zh-CN" sz="1600" dirty="0">
+              <a:solidFill>
+                <a:srgbClr val="808080">
+                  <a:alpha val="19999"/>
+                </a:srgbClr>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="SimSun"/>
+            </a:rPr>
+            <a:t>AI 生成</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing_wm3.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:absoluteAnchor>
     <xdr:pos x="6800000" y="6400000"/>
@@ -477,7 +621,151 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing_wm4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:absoluteAnchor>
+    <xdr:pos x="6800000" y="6400000"/>
+    <xdr:ext cx="2200000" cy="350000"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1" name="Watermark"/>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="0">
+          <a:off x="0" y="0"/>
+          <a:ext cx="2200000" cy="350000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" rtlCol="0" anchor="b" lIns="0" tIns="0" rIns="0" bIns="0"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="r"/>
+          <a:r>
+            <a:rPr lang="zh-CN" sz="1600" dirty="0">
+              <a:solidFill>
+                <a:srgbClr val="808080">
+                  <a:alpha val="19999"/>
+                </a:srgbClr>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="SimSun"/>
+            </a:rPr>
+            <a:t>AI 生成</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/drawings/drawing_wm5.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:absoluteAnchor>
+    <xdr:pos x="6800000" y="6400000"/>
+    <xdr:ext cx="2200000" cy="350000"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1" name="Watermark"/>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="0">
+          <a:off x="0" y="0"/>
+          <a:ext cx="2200000" cy="350000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" rtlCol="0" anchor="b" lIns="0" tIns="0" rIns="0" bIns="0"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="r"/>
+          <a:r>
+            <a:rPr lang="zh-CN" sz="1600" dirty="0">
+              <a:solidFill>
+                <a:srgbClr val="808080">
+                  <a:alpha val="19999"/>
+                </a:srgbClr>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="SimSun"/>
+            </a:rPr>
+            <a:t>AI 生成</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing_wm5.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:absoluteAnchor>
+    <xdr:pos x="6800000" y="6400000"/>
+    <xdr:ext cx="2200000" cy="350000"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1" name="Watermark"/>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="0">
+          <a:off x="0" y="0"/>
+          <a:ext cx="2200000" cy="350000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" rtlCol="0" anchor="b" lIns="0" tIns="0" rIns="0" bIns="0"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="r"/>
+          <a:r>
+            <a:rPr lang="zh-CN" sz="1600" dirty="0">
+              <a:solidFill>
+                <a:srgbClr val="808080">
+                  <a:alpha val="19999"/>
+                </a:srgbClr>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="SimSun"/>
+            </a:rPr>
+            <a:t>AI 生成</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing_wm6.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:absoluteAnchor>
     <xdr:pos x="6800000" y="6400000"/>
@@ -5140,7 +5428,7 @@
       </c>
       <c r="J9" s="5" t="inlineStr">
         <is>
-          <t>天融信CHM:配置访问控制策略；PA:Datasheet 规格表</t>
+          <t>天融信CHM:配置访问控制策略[toc450050600]；PA:PA-3400 Series Datasheet 2026-02-26（资料登记表#15，URL留档）</t>
         </is>
       </c>
       <c r="K9" s="5" t="inlineStr">
@@ -7078,7 +7366,7 @@
       </c>
       <c r="L41" s="5" t="inlineStr">
         <is>
-          <t>R13-R21 九大国际应用全部登记实测（T7用例）</t>
+          <t>R13-R21 九大国际应用全部登记实测（T7用例）（V12/V74）</t>
         </is>
       </c>
     </row>
@@ -8588,7 +8876,7 @@
       </c>
       <c r="J67" s="5" t="inlineStr">
         <is>
-          <t>双侧手册均无量化数据</t>
+          <t>双侧手册全文检索无量化数据（P3否定证据留痕 report_D.txt）；建议50站点抽样（V清单）</t>
         </is>
       </c>
       <c r="K67" s="5" t="inlineStr">
@@ -8598,7 +8886,7 @@
       </c>
       <c r="L67" s="5" t="inlineStr">
         <is>
-          <t>R46 抽样实测国内站点分类准确率（港澳场景关键项，建议50站点抽样）</t>
+          <t>R46 抽样实测国内站点分类准确率（港澳场景关键项，建议50站点抽样）（V24）</t>
         </is>
       </c>
     </row>
@@ -11404,7 +11692,7 @@
       </c>
       <c r="J115" s="5" t="inlineStr">
         <is>
-          <t>双侧手册均无资质证书信息</t>
+          <t>双侧手册均无资质证书信息（P3全文检索无命中）；天融信查公安部目录、港澳准入另行核实（V54）</t>
         </is>
       </c>
       <c r="K115" s="5" t="inlineStr">
@@ -11590,7 +11878,7 @@
       </c>
       <c r="J118" s="4" t="inlineStr">
         <is>
-          <t>双侧手册均无信创目录信息；天融信需查官方信创目录</t>
+          <t>双侧手册均无信创目录信息（P3全文检索无命中，否定证据）；天融信需查官方信创目录（V57）</t>
         </is>
       </c>
       <c r="K118" s="4" t="inlineStr">
@@ -11600,7 +11888,7 @@
       </c>
       <c r="L118" s="4" t="inlineStr">
         <is>
-          <t>R65(已有) 天融信信创目录状态需核实</t>
+          <t>R65(已有) 天融信信创目录状态需核实（V57）</t>
         </is>
       </c>
     </row>
@@ -11786,7 +12074,7 @@
       </c>
       <c r="L121" s="5" t="inlineStr">
         <is>
-          <t>R69 双方行业准入资质包（金融/运营商/关基）需商务渠道核实</t>
+          <t>R69 双方行业准入资质包（金融/运营商/关基）需商务渠道核实（V59）</t>
         </is>
       </c>
     </row>
@@ -11968,7 +12256,7 @@
       </c>
       <c r="L124" s="9" t="inlineStr">
         <is>
-          <t>P3填充</t>
+          <t>天融信ECMP待读CHM路由正文确认（V61）</t>
         </is>
       </c>
     </row>
@@ -12138,7 +12426,7 @@
       </c>
       <c r="J127" s="9" t="inlineStr">
         <is>
-          <t>PA:Web帮助&gt;Network Profiles&gt;MACsec(11.1)</t>
+          <t>天融信CHM:全文检索无命中（P3否定证据留痕）；PA:Web帮助&gt;Network Profiles&gt;MACsec(11.1)</t>
         </is>
       </c>
       <c r="K127" s="9" t="inlineStr">

--- a/天融信vsPA功能对比.xlsx
+++ b/天融信vsPA功能对比.xlsx
@@ -381,6 +381,54 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing_wm1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:absoluteAnchor>
+    <xdr:pos x="6800000" y="6400000"/>
+    <xdr:ext cx="2200000" cy="350000"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1" name="Watermark"/>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="0">
+          <a:off x="0" y="0"/>
+          <a:ext cx="2200000" cy="350000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" rtlCol="0" anchor="b" lIns="0" tIns="0" rIns="0" bIns="0"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="r"/>
+          <a:r>
+            <a:rPr lang="zh-CN" sz="1600" dirty="0">
+              <a:solidFill>
+                <a:srgbClr val="808080">
+                  <a:alpha val="19999"/>
+                </a:srgbClr>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="SimSun"/>
+            </a:rPr>
+            <a:t>AI 生成</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/drawings/drawing_wm2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:absoluteAnchor>
@@ -430,6 +478,102 @@
 </file>
 
 <file path=xl/drawings/drawing_wm2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:absoluteAnchor>
+    <xdr:pos x="6800000" y="6400000"/>
+    <xdr:ext cx="2200000" cy="350000"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1" name="Watermark"/>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="0">
+          <a:off x="0" y="0"/>
+          <a:ext cx="2200000" cy="350000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" rtlCol="0" anchor="b" lIns="0" tIns="0" rIns="0" bIns="0"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="r"/>
+          <a:r>
+            <a:rPr lang="zh-CN" sz="1600" dirty="0">
+              <a:solidFill>
+                <a:srgbClr val="808080">
+                  <a:alpha val="19999"/>
+                </a:srgbClr>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="SimSun"/>
+            </a:rPr>
+            <a:t>AI 生成</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing_wm2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:absoluteAnchor>
+    <xdr:pos x="6800000" y="6400000"/>
+    <xdr:ext cx="2200000" cy="350000"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1" name="Watermark"/>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="0">
+          <a:off x="0" y="0"/>
+          <a:ext cx="2200000" cy="350000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" rtlCol="0" anchor="b" lIns="0" tIns="0" rIns="0" bIns="0"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="r"/>
+          <a:r>
+            <a:rPr lang="zh-CN" sz="1600" dirty="0">
+              <a:solidFill>
+                <a:srgbClr val="808080">
+                  <a:alpha val="19999"/>
+                </a:srgbClr>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="SimSun"/>
+            </a:rPr>
+            <a:t>AI 生成</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing_wm3.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:absoluteAnchor>
     <xdr:pos x="6800000" y="6400000"/>
@@ -669,6 +813,54 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing_wm4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:absoluteAnchor>
+    <xdr:pos x="6800000" y="6400000"/>
+    <xdr:ext cx="2200000" cy="350000"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1" name="Watermark"/>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="0">
+          <a:off x="0" y="0"/>
+          <a:ext cx="2200000" cy="350000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" rtlCol="0" anchor="b" lIns="0" tIns="0" rIns="0" bIns="0"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="r"/>
+          <a:r>
+            <a:rPr lang="zh-CN" sz="1600" dirty="0">
+              <a:solidFill>
+                <a:srgbClr val="808080">
+                  <a:alpha val="19999"/>
+                </a:srgbClr>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="SimSun"/>
+            </a:rPr>
+            <a:t>AI 生成</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/drawings/drawing_wm5.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:absoluteAnchor>
@@ -718,6 +910,102 @@
 </file>
 
 <file path=xl/drawings/drawing_wm5.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:absoluteAnchor>
+    <xdr:pos x="6800000" y="6400000"/>
+    <xdr:ext cx="2200000" cy="350000"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1" name="Watermark"/>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="0">
+          <a:off x="0" y="0"/>
+          <a:ext cx="2200000" cy="350000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" rtlCol="0" anchor="b" lIns="0" tIns="0" rIns="0" bIns="0"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="r"/>
+          <a:r>
+            <a:rPr lang="zh-CN" sz="1600" dirty="0">
+              <a:solidFill>
+                <a:srgbClr val="808080">
+                  <a:alpha val="19999"/>
+                </a:srgbClr>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="SimSun"/>
+            </a:rPr>
+            <a:t>AI 生成</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing_wm5.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:absoluteAnchor>
+    <xdr:pos x="6800000" y="6400000"/>
+    <xdr:ext cx="2200000" cy="350000"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1" name="Watermark"/>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="0">
+          <a:off x="0" y="0"/>
+          <a:ext cx="2200000" cy="350000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" rtlCol="0" anchor="b" lIns="0" tIns="0" rIns="0" bIns="0"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="r"/>
+          <a:r>
+            <a:rPr lang="zh-CN" sz="1600" dirty="0">
+              <a:solidFill>
+                <a:srgbClr val="808080">
+                  <a:alpha val="19999"/>
+                </a:srgbClr>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="SimSun"/>
+            </a:rPr>
+            <a:t>AI 生成</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing_wm6.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:absoluteAnchor>
     <xdr:pos x="6800000" y="6400000"/>

--- a/天融信vsPA功能对比.xlsx
+++ b/天融信vsPA功能对比.xlsx
@@ -285,870 +285,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing_wm1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:absoluteAnchor>
-    <xdr:pos x="6800000" y="6400000"/>
-    <xdr:ext cx="2200000" cy="350000"/>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="1" name="Watermark"/>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm rot="0">
-          <a:off x="0" y="0"/>
-          <a:ext cx="2200000" cy="350000"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:txBody>
-        <a:bodyPr wrap="square" rtlCol="0" anchor="b" lIns="0" tIns="0" rIns="0" bIns="0"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="r"/>
-          <a:r>
-            <a:rPr lang="zh-CN" sz="1600" dirty="0">
-              <a:solidFill>
-                <a:srgbClr val="808080">
-                  <a:alpha val="19999"/>
-                </a:srgbClr>
-              </a:solidFill>
-              <a:latin typeface="Arial"/>
-              <a:ea typeface="SimSun"/>
-            </a:rPr>
-            <a:t>AI 生成</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:absoluteAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing_wm1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:absoluteAnchor>
-    <xdr:pos x="6800000" y="6400000"/>
-    <xdr:ext cx="2200000" cy="350000"/>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="1" name="Watermark"/>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm rot="0">
-          <a:off x="0" y="0"/>
-          <a:ext cx="2200000" cy="350000"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:txBody>
-        <a:bodyPr wrap="square" rtlCol="0" anchor="b" lIns="0" tIns="0" rIns="0" bIns="0"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="r"/>
-          <a:r>
-            <a:rPr lang="zh-CN" sz="1600" dirty="0">
-              <a:solidFill>
-                <a:srgbClr val="808080">
-                  <a:alpha val="19999"/>
-                </a:srgbClr>
-              </a:solidFill>
-              <a:latin typeface="Arial"/>
-              <a:ea typeface="SimSun"/>
-            </a:rPr>
-            <a:t>AI 生成</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:absoluteAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing_wm1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:absoluteAnchor>
-    <xdr:pos x="6800000" y="6400000"/>
-    <xdr:ext cx="2200000" cy="350000"/>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="1" name="Watermark"/>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm rot="0">
-          <a:off x="0" y="0"/>
-          <a:ext cx="2200000" cy="350000"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:txBody>
-        <a:bodyPr wrap="square" rtlCol="0" anchor="b" lIns="0" tIns="0" rIns="0" bIns="0"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="r"/>
-          <a:r>
-            <a:rPr lang="zh-CN" sz="1600" dirty="0">
-              <a:solidFill>
-                <a:srgbClr val="808080">
-                  <a:alpha val="19999"/>
-                </a:srgbClr>
-              </a:solidFill>
-              <a:latin typeface="Arial"/>
-              <a:ea typeface="SimSun"/>
-            </a:rPr>
-            <a:t>AI 生成</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:absoluteAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing_wm2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:absoluteAnchor>
-    <xdr:pos x="6800000" y="6400000"/>
-    <xdr:ext cx="2200000" cy="350000"/>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="1" name="Watermark"/>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm rot="0">
-          <a:off x="0" y="0"/>
-          <a:ext cx="2200000" cy="350000"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:txBody>
-        <a:bodyPr wrap="square" rtlCol="0" anchor="b" lIns="0" tIns="0" rIns="0" bIns="0"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="r"/>
-          <a:r>
-            <a:rPr lang="zh-CN" sz="1600" dirty="0">
-              <a:solidFill>
-                <a:srgbClr val="808080">
-                  <a:alpha val="19999"/>
-                </a:srgbClr>
-              </a:solidFill>
-              <a:latin typeface="Arial"/>
-              <a:ea typeface="SimSun"/>
-            </a:rPr>
-            <a:t>AI 生成</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:absoluteAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing_wm2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:absoluteAnchor>
-    <xdr:pos x="6800000" y="6400000"/>
-    <xdr:ext cx="2200000" cy="350000"/>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="1" name="Watermark"/>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm rot="0">
-          <a:off x="0" y="0"/>
-          <a:ext cx="2200000" cy="350000"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:txBody>
-        <a:bodyPr wrap="square" rtlCol="0" anchor="b" lIns="0" tIns="0" rIns="0" bIns="0"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="r"/>
-          <a:r>
-            <a:rPr lang="zh-CN" sz="1600" dirty="0">
-              <a:solidFill>
-                <a:srgbClr val="808080">
-                  <a:alpha val="19999"/>
-                </a:srgbClr>
-              </a:solidFill>
-              <a:latin typeface="Arial"/>
-              <a:ea typeface="SimSun"/>
-            </a:rPr>
-            <a:t>AI 生成</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:absoluteAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing_wm2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:absoluteAnchor>
-    <xdr:pos x="6800000" y="6400000"/>
-    <xdr:ext cx="2200000" cy="350000"/>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="1" name="Watermark"/>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm rot="0">
-          <a:off x="0" y="0"/>
-          <a:ext cx="2200000" cy="350000"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:txBody>
-        <a:bodyPr wrap="square" rtlCol="0" anchor="b" lIns="0" tIns="0" rIns="0" bIns="0"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="r"/>
-          <a:r>
-            <a:rPr lang="zh-CN" sz="1600" dirty="0">
-              <a:solidFill>
-                <a:srgbClr val="808080">
-                  <a:alpha val="19999"/>
-                </a:srgbClr>
-              </a:solidFill>
-              <a:latin typeface="Arial"/>
-              <a:ea typeface="SimSun"/>
-            </a:rPr>
-            <a:t>AI 生成</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:absoluteAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing_wm3.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:absoluteAnchor>
-    <xdr:pos x="6800000" y="6400000"/>
-    <xdr:ext cx="2200000" cy="350000"/>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="1" name="Watermark"/>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm rot="0">
-          <a:off x="0" y="0"/>
-          <a:ext cx="2200000" cy="350000"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:txBody>
-        <a:bodyPr wrap="square" rtlCol="0" anchor="b" lIns="0" tIns="0" rIns="0" bIns="0"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="r"/>
-          <a:r>
-            <a:rPr lang="zh-CN" sz="1600" dirty="0">
-              <a:solidFill>
-                <a:srgbClr val="808080">
-                  <a:alpha val="19999"/>
-                </a:srgbClr>
-              </a:solidFill>
-              <a:latin typeface="Arial"/>
-              <a:ea typeface="SimSun"/>
-            </a:rPr>
-            <a:t>AI 生成</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:absoluteAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing_wm3.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:absoluteAnchor>
-    <xdr:pos x="6800000" y="6400000"/>
-    <xdr:ext cx="2200000" cy="350000"/>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="1" name="Watermark"/>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm rot="0">
-          <a:off x="0" y="0"/>
-          <a:ext cx="2200000" cy="350000"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:txBody>
-        <a:bodyPr wrap="square" rtlCol="0" anchor="b" lIns="0" tIns="0" rIns="0" bIns="0"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="r"/>
-          <a:r>
-            <a:rPr lang="zh-CN" sz="1600" dirty="0">
-              <a:solidFill>
-                <a:srgbClr val="808080">
-                  <a:alpha val="19999"/>
-                </a:srgbClr>
-              </a:solidFill>
-              <a:latin typeface="Arial"/>
-              <a:ea typeface="SimSun"/>
-            </a:rPr>
-            <a:t>AI 生成</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:absoluteAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing_wm3.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:absoluteAnchor>
-    <xdr:pos x="6800000" y="6400000"/>
-    <xdr:ext cx="2200000" cy="350000"/>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="1" name="Watermark"/>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm rot="0">
-          <a:off x="0" y="0"/>
-          <a:ext cx="2200000" cy="350000"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:txBody>
-        <a:bodyPr wrap="square" rtlCol="0" anchor="b" lIns="0" tIns="0" rIns="0" bIns="0"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="r"/>
-          <a:r>
-            <a:rPr lang="zh-CN" sz="1600" dirty="0">
-              <a:solidFill>
-                <a:srgbClr val="808080">
-                  <a:alpha val="19999"/>
-                </a:srgbClr>
-              </a:solidFill>
-              <a:latin typeface="Arial"/>
-              <a:ea typeface="SimSun"/>
-            </a:rPr>
-            <a:t>AI 生成</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:absoluteAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing_wm4.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:absoluteAnchor>
-    <xdr:pos x="6800000" y="6400000"/>
-    <xdr:ext cx="2200000" cy="350000"/>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="1" name="Watermark"/>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm rot="0">
-          <a:off x="0" y="0"/>
-          <a:ext cx="2200000" cy="350000"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:txBody>
-        <a:bodyPr wrap="square" rtlCol="0" anchor="b" lIns="0" tIns="0" rIns="0" bIns="0"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="r"/>
-          <a:r>
-            <a:rPr lang="zh-CN" sz="1600" dirty="0">
-              <a:solidFill>
-                <a:srgbClr val="808080">
-                  <a:alpha val="19999"/>
-                </a:srgbClr>
-              </a:solidFill>
-              <a:latin typeface="Arial"/>
-              <a:ea typeface="SimSun"/>
-            </a:rPr>
-            <a:t>AI 生成</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:absoluteAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing_wm4.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:absoluteAnchor>
-    <xdr:pos x="6800000" y="6400000"/>
-    <xdr:ext cx="2200000" cy="350000"/>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="1" name="Watermark"/>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm rot="0">
-          <a:off x="0" y="0"/>
-          <a:ext cx="2200000" cy="350000"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:txBody>
-        <a:bodyPr wrap="square" rtlCol="0" anchor="b" lIns="0" tIns="0" rIns="0" bIns="0"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="r"/>
-          <a:r>
-            <a:rPr lang="zh-CN" sz="1600" dirty="0">
-              <a:solidFill>
-                <a:srgbClr val="808080">
-                  <a:alpha val="19999"/>
-                </a:srgbClr>
-              </a:solidFill>
-              <a:latin typeface="Arial"/>
-              <a:ea typeface="SimSun"/>
-            </a:rPr>
-            <a:t>AI 生成</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:absoluteAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing_wm4.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:absoluteAnchor>
-    <xdr:pos x="6800000" y="6400000"/>
-    <xdr:ext cx="2200000" cy="350000"/>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="1" name="Watermark"/>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm rot="0">
-          <a:off x="0" y="0"/>
-          <a:ext cx="2200000" cy="350000"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:txBody>
-        <a:bodyPr wrap="square" rtlCol="0" anchor="b" lIns="0" tIns="0" rIns="0" bIns="0"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="r"/>
-          <a:r>
-            <a:rPr lang="zh-CN" sz="1600" dirty="0">
-              <a:solidFill>
-                <a:srgbClr val="808080">
-                  <a:alpha val="19999"/>
-                </a:srgbClr>
-              </a:solidFill>
-              <a:latin typeface="Arial"/>
-              <a:ea typeface="SimSun"/>
-            </a:rPr>
-            <a:t>AI 生成</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:absoluteAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing_wm5.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:absoluteAnchor>
-    <xdr:pos x="6800000" y="6400000"/>
-    <xdr:ext cx="2200000" cy="350000"/>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="1" name="Watermark"/>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm rot="0">
-          <a:off x="0" y="0"/>
-          <a:ext cx="2200000" cy="350000"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:txBody>
-        <a:bodyPr wrap="square" rtlCol="0" anchor="b" lIns="0" tIns="0" rIns="0" bIns="0"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="r"/>
-          <a:r>
-            <a:rPr lang="zh-CN" sz="1600" dirty="0">
-              <a:solidFill>
-                <a:srgbClr val="808080">
-                  <a:alpha val="19999"/>
-                </a:srgbClr>
-              </a:solidFill>
-              <a:latin typeface="Arial"/>
-              <a:ea typeface="SimSun"/>
-            </a:rPr>
-            <a:t>AI 生成</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:absoluteAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing_wm5.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:absoluteAnchor>
-    <xdr:pos x="6800000" y="6400000"/>
-    <xdr:ext cx="2200000" cy="350000"/>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="1" name="Watermark"/>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm rot="0">
-          <a:off x="0" y="0"/>
-          <a:ext cx="2200000" cy="350000"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:txBody>
-        <a:bodyPr wrap="square" rtlCol="0" anchor="b" lIns="0" tIns="0" rIns="0" bIns="0"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="r"/>
-          <a:r>
-            <a:rPr lang="zh-CN" sz="1600" dirty="0">
-              <a:solidFill>
-                <a:srgbClr val="808080">
-                  <a:alpha val="19999"/>
-                </a:srgbClr>
-              </a:solidFill>
-              <a:latin typeface="Arial"/>
-              <a:ea typeface="SimSun"/>
-            </a:rPr>
-            <a:t>AI 生成</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:absoluteAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing_wm5.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:absoluteAnchor>
-    <xdr:pos x="6800000" y="6400000"/>
-    <xdr:ext cx="2200000" cy="350000"/>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="1" name="Watermark"/>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm rot="0">
-          <a:off x="0" y="0"/>
-          <a:ext cx="2200000" cy="350000"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:txBody>
-        <a:bodyPr wrap="square" rtlCol="0" anchor="b" lIns="0" tIns="0" rIns="0" bIns="0"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="r"/>
-          <a:r>
-            <a:rPr lang="zh-CN" sz="1600" dirty="0">
-              <a:solidFill>
-                <a:srgbClr val="808080">
-                  <a:alpha val="19999"/>
-                </a:srgbClr>
-              </a:solidFill>
-              <a:latin typeface="Arial"/>
-              <a:ea typeface="SimSun"/>
-            </a:rPr>
-            <a:t>AI 生成</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:absoluteAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing_wm6.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:absoluteAnchor>
-    <xdr:pos x="6800000" y="6400000"/>
-    <xdr:ext cx="2200000" cy="350000"/>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="1" name="Watermark"/>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm rot="0">
-          <a:off x="0" y="0"/>
-          <a:ext cx="2200000" cy="350000"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:txBody>
-        <a:bodyPr wrap="square" rtlCol="0" anchor="b" lIns="0" tIns="0" rIns="0" bIns="0"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="r"/>
-          <a:r>
-            <a:rPr lang="zh-CN" sz="1600" dirty="0">
-              <a:solidFill>
-                <a:srgbClr val="808080">
-                  <a:alpha val="19999"/>
-                </a:srgbClr>
-              </a:solidFill>
-              <a:latin typeface="Arial"/>
-              <a:ea typeface="SimSun"/>
-            </a:rPr>
-            <a:t>AI 生成</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:absoluteAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing_wm6.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:absoluteAnchor>
-    <xdr:pos x="6800000" y="6400000"/>
-    <xdr:ext cx="2200000" cy="350000"/>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="1" name="Watermark"/>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm rot="0">
-          <a:off x="0" y="0"/>
-          <a:ext cx="2200000" cy="350000"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:txBody>
-        <a:bodyPr wrap="square" rtlCol="0" anchor="b" lIns="0" tIns="0" rIns="0" bIns="0"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="r"/>
-          <a:r>
-            <a:rPr lang="zh-CN" sz="1600" dirty="0">
-              <a:solidFill>
-                <a:srgbClr val="808080">
-                  <a:alpha val="19999"/>
-                </a:srgbClr>
-              </a:solidFill>
-              <a:latin typeface="Arial"/>
-              <a:ea typeface="SimSun"/>
-            </a:rPr>
-            <a:t>AI 生成</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:absoluteAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing_wm6.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:absoluteAnchor>
-    <xdr:pos x="6800000" y="6400000"/>
-    <xdr:ext cx="2200000" cy="350000"/>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="1" name="Watermark"/>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm rot="0">
-          <a:off x="0" y="0"/>
-          <a:ext cx="2200000" cy="350000"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:txBody>
-        <a:bodyPr wrap="square" rtlCol="0" anchor="b" lIns="0" tIns="0" rIns="0" bIns="0"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="r"/>
-          <a:r>
-            <a:rPr lang="zh-CN" sz="1600" dirty="0">
-              <a:solidFill>
-                <a:srgbClr val="808080">
-                  <a:alpha val="19999"/>
-                </a:srgbClr>
-              </a:solidFill>
-              <a:latin typeface="Arial"/>
-              <a:ea typeface="SimSun"/>
-            </a:rPr>
-            <a:t>AI 生成</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:absoluteAnchor>
-</xdr:wsDr>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -1433,7 +569,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
@@ -1602,7 +738,7 @@
       </c>
       <c r="M4" s="4" t="inlineStr">
         <is>
-          <t>[R1→主证据矩阵#84] 天融信CHM:日志配置[toc490041759]+日志服务器配置[ref465084227]+日志存储管理[topic212]；PA:webhelp p305/p808/p817/p721，admin p579/p589</t>
+          <t>[R1→M#84] ; TS:日志配置[e:toc490041759] + 日志服务器配置[e:ref465084227] + 日志存储管理[e:topic212] ; PA-WEBHELP:[p:305][p:808][p:817][p:721] ; PA-ADMIN:[p:579][p:589]</t>
         </is>
       </c>
       <c r="N4" s="4" t="inlineStr">
@@ -1674,7 +810,7 @@
       </c>
       <c r="M5" s="5" t="inlineStr">
         <is>
-          <t>[R2→主证据矩阵#83] 天融信CHM:功能和特点[toc462736546]第三方管理接口+与态势感知系统联动[-ngfw]；PA:admin p125/p854-858，webhelp p628/p731-732</t>
+          <t>[R2→M#83] ; TS:功能和特点[e:toc462736546] + 与态势感知系统联动[e:-ngfw] ; PA-WEBHELP:[p:628][p:731-732] ; PA-ADMIN:[p:125][p:854-858]</t>
         </is>
       </c>
       <c r="N5" s="5" t="inlineStr">
@@ -1734,7 +870,7 @@
       </c>
       <c r="M6" s="4" t="inlineStr">
         <is>
-          <t>[R3→主证据矩阵#83] 天融信CHM:功能和特点[toc462736546]第三方管理接口+与态势感知系统联动[-ngfw]；PA:admin p125/p854-858，webhelp p628/p731-732</t>
+          <t>[R3→M#83] ; TS:功能和特点[e:toc462736546] + 与态势感知系统联动[e:-ngfw] ; PA-WEBHELP:[p:628][p:731-732] ; PA-ADMIN:[p:125][p:854-858]</t>
         </is>
       </c>
       <c r="N6" s="4" t="inlineStr">
@@ -1794,7 +930,7 @@
       </c>
       <c r="M7" s="5" t="inlineStr">
         <is>
-          <t>[R4→主证据矩阵#83] 天融信CHM:功能和特点[toc462736546]第三方管理接口+与态势感知系统联动[-ngfw]；PA:admin p125/p854-858，webhelp p628/p731-732</t>
+          <t>[R4→M#83] ; TS:功能和特点[e:toc462736546] + 与态势感知系统联动[e:-ngfw] ; PA-WEBHELP:[p:628][p:731-732] ; PA-ADMIN:[p:125][p:854-858]</t>
         </is>
       </c>
       <c r="N7" s="5" t="inlineStr">
@@ -1866,7 +1002,7 @@
       </c>
       <c r="M8" s="4" t="inlineStr">
         <is>
-          <t>[R5→主证据矩阵#84] 天融信CHM:日志配置[toc490041759]+日志服务器配置[ref465084227]+日志存储管理[topic212]；PA:webhelp p305/p808/p817/p721，admin p579/p589</t>
+          <t>[R5→M#84] ; TS:日志配置[e:toc490041759] + 日志服务器配置[e:ref465084227] + 日志存储管理[e:topic212] ; PA-WEBHELP:[p:305][p:808][p:817][p:721] ; PA-ADMIN:[p:579][p:589]</t>
         </is>
       </c>
       <c r="N8" s="4" t="inlineStr">
@@ -1926,7 +1062,7 @@
       </c>
       <c r="M9" s="5" t="inlineStr">
         <is>
-          <t>[R6→主证据矩阵#84] 天融信CHM:日志配置[toc490041759]+日志服务器配置[ref465084227]+日志存储管理[topic212]；PA:webhelp p305/p808/p817/p721，admin p579/p589</t>
+          <t>[R6→M#84] ; TS:日志配置[e:toc490041759] + 日志服务器配置[e:ref465084227] + 日志存储管理[e:topic212] ; PA-WEBHELP:[p:305][p:808][p:817][p:721] ; PA-ADMIN:[p:579][p:589]</t>
         </is>
       </c>
       <c r="N9" s="5" t="inlineStr">
@@ -1986,7 +1122,7 @@
       </c>
       <c r="M10" s="4" t="inlineStr">
         <is>
-          <t>[R7→主证据矩阵#84] 天融信CHM:日志配置[toc490041759]+日志服务器配置[ref465084227]+日志存储管理[topic212]；PA:webhelp p305/p808/p817/p721，admin p579/p589</t>
+          <t>[R7→M#84] ; TS:日志配置[e:toc490041759] + 日志服务器配置[e:ref465084227] + 日志存储管理[e:topic212] ; PA-WEBHELP:[p:305][p:808][p:817][p:721] ; PA-ADMIN:[p:579][p:589]</t>
         </is>
       </c>
       <c r="N10" s="4" t="inlineStr">
@@ -2046,7 +1182,7 @@
       </c>
       <c r="M11" s="5" t="inlineStr">
         <is>
-          <t>[R8→主证据矩阵#84] 天融信CHM:日志配置[toc490041759]+日志服务器配置[ref465084227]+日志存储管理[topic212]；PA:webhelp p305/p808/p817/p721，admin p579/p589</t>
+          <t>[R8→M#84] ; TS:日志配置[e:toc490041759] + 日志服务器配置[e:ref465084227] + 日志存储管理[e:topic212] ; PA-WEBHELP:[p:305][p:808][p:817][p:721] ; PA-ADMIN:[p:579][p:589]</t>
         </is>
       </c>
       <c r="N11" s="5" t="inlineStr">
@@ -2102,7 +1238,7 @@
       </c>
       <c r="M12" s="4" t="inlineStr">
         <is>
-          <t>[R9→主证据矩阵#84] 天融信CHM:日志配置[toc490041759]+日志服务器配置[ref465084227]+日志存储管理[topic212]；PA:webhelp p305/p808/p817/p721，admin p579/p589</t>
+          <t>[R9→M#84] ; TS:日志配置[e:toc490041759] + 日志服务器配置[e:ref465084227] + 日志存储管理[e:topic212] ; PA-WEBHELP:[p:305][p:808][p:817][p:721] ; PA-ADMIN:[p:579][p:589]</t>
         </is>
       </c>
       <c r="N12" s="4" t="inlineStr">
@@ -2158,7 +1294,7 @@
       </c>
       <c r="M13" s="5" t="inlineStr">
         <is>
-          <t>[R10→主证据矩阵#84] 天融信CHM:日志配置[toc490041759]+日志服务器配置[ref465084227]+日志存储管理[topic212]；PA:webhelp p305/p808/p817/p721，admin p579/p589</t>
+          <t>[R10→M#84] ; TS:日志配置[e:toc490041759] + 日志服务器配置[e:ref465084227] + 日志存储管理[e:topic212] ; PA-WEBHELP:[p:305][p:808][p:817][p:721] ; PA-ADMIN:[p:579][p:589]</t>
         </is>
       </c>
       <c r="N13" s="5" t="inlineStr">
@@ -2214,7 +1350,7 @@
       </c>
       <c r="M14" s="4" t="inlineStr">
         <is>
-          <t>[R11→主证据矩阵#84] 天融信CHM:日志配置[toc490041759]+日志服务器配置[ref465084227]+日志存储管理[topic212]；PA:webhelp p305/p808/p817/p721，admin p579/p589</t>
+          <t>[R11→M#84] ; TS:日志配置[e:toc490041759] + 日志服务器配置[e:ref465084227] + 日志存储管理[e:topic212] ; PA-WEBHELP:[p:305][p:808][p:817][p:721] ; PA-ADMIN:[p:579][p:589]</t>
         </is>
       </c>
       <c r="N14" s="4" t="inlineStr">
@@ -2286,7 +1422,7 @@
       </c>
       <c r="M15" s="5" t="inlineStr">
         <is>
-          <t>[R12→主证据矩阵#91] 天融信CHM:选项[topic206]License升级；PA:webhelp p851，admin p76-78</t>
+          <t>[R12→M#91] ; TS:选项[e:topic206] + License升级 ; PA-WEBHELP:[p:851] ; PA-ADMIN:[p:76-78]</t>
         </is>
       </c>
       <c r="N15" s="5" t="inlineStr">
@@ -2358,7 +1494,7 @@
       </c>
       <c r="M16" s="4" t="inlineStr">
         <is>
-          <t>[R13→主证据矩阵#24] 天融信CHM:应用[toc448912175]；PA:admin p889-940 App-ID</t>
+          <t>[R13→M#24] ; TS:应用[e:toc448912175] ; PA-ADMIN:[p:889-940] ; PA-NOTE:App-ID</t>
         </is>
       </c>
       <c r="N16" s="4" t="inlineStr">
@@ -2414,7 +1550,7 @@
       </c>
       <c r="M17" s="5" t="inlineStr">
         <is>
-          <t>[R14→主证据矩阵#24] 天融信CHM:应用[toc448912175]；PA:admin p889-940 App-ID</t>
+          <t>[R14→M#24] ; TS:应用[e:toc448912175] ; PA-ADMIN:[p:889-940] ; PA-NOTE:App-ID</t>
         </is>
       </c>
       <c r="N17" s="5" t="inlineStr">
@@ -2470,7 +1606,7 @@
       </c>
       <c r="M18" s="4" t="inlineStr">
         <is>
-          <t>[R15→主证据矩阵#24] 天融信CHM:应用[toc448912175]；PA:admin p889-940 App-ID</t>
+          <t>[R15→M#24] ; TS:应用[e:toc448912175] ; PA-ADMIN:[p:889-940] ; PA-NOTE:App-ID</t>
         </is>
       </c>
       <c r="N18" s="4" t="inlineStr">
@@ -2526,7 +1662,7 @@
       </c>
       <c r="M19" s="5" t="inlineStr">
         <is>
-          <t>[R16→主证据矩阵#24] 天融信CHM:应用[toc448912175]；PA:admin p889-940 App-ID</t>
+          <t>[R16→M#24] ; TS:应用[e:toc448912175] ; PA-ADMIN:[p:889-940] ; PA-NOTE:App-ID</t>
         </is>
       </c>
       <c r="N19" s="5" t="inlineStr">
@@ -2582,7 +1718,7 @@
       </c>
       <c r="M20" s="4" t="inlineStr">
         <is>
-          <t>[R17→主证据矩阵#24] 天融信CHM:应用[toc448912175]；PA:admin p889-940 App-ID</t>
+          <t>[R17→M#24] ; TS:应用[e:toc448912175] ; PA-ADMIN:[p:889-940] ; PA-NOTE:App-ID</t>
         </is>
       </c>
       <c r="N20" s="4" t="inlineStr">
@@ -2638,7 +1774,7 @@
       </c>
       <c r="M21" s="5" t="inlineStr">
         <is>
-          <t>[R18→主证据矩阵#24] 天融信CHM:应用[toc448912175]；PA:admin p889-940 App-ID</t>
+          <t>[R18→M#24] ; TS:应用[e:toc448912175] ; PA-ADMIN:[p:889-940] ; PA-NOTE:App-ID</t>
         </is>
       </c>
       <c r="N21" s="5" t="inlineStr">
@@ -2694,7 +1830,7 @@
       </c>
       <c r="M22" s="4" t="inlineStr">
         <is>
-          <t>[R19→主证据矩阵#24] 天融信CHM:应用[toc448912175]；PA:admin p889-940 App-ID</t>
+          <t>[R19→M#24] ; TS:应用[e:toc448912175] ; PA-ADMIN:[p:889-940] ; PA-NOTE:App-ID</t>
         </is>
       </c>
       <c r="N22" s="4" t="inlineStr">
@@ -2750,7 +1886,7 @@
       </c>
       <c r="M23" s="5" t="inlineStr">
         <is>
-          <t>[R20→主证据矩阵#24] 天融信CHM:应用[toc448912175]；PA:admin p889-940 App-ID</t>
+          <t>[R20→M#24] ; TS:应用[e:toc448912175] ; PA-ADMIN:[p:889-940] ; PA-NOTE:App-ID</t>
         </is>
       </c>
       <c r="N23" s="5" t="inlineStr">
@@ -2806,7 +1942,7 @@
       </c>
       <c r="M24" s="4" t="inlineStr">
         <is>
-          <t>[R21→主证据矩阵#24] 天融信CHM:应用[toc448912175]；PA:admin p889-940 App-ID</t>
+          <t>[R21→M#24] ; TS:应用[e:toc448912175] ; PA-ADMIN:[p:889-940] ; PA-NOTE:App-ID</t>
         </is>
       </c>
       <c r="N24" s="4" t="inlineStr">
@@ -2878,7 +2014,7 @@
       </c>
       <c r="M25" s="5" t="inlineStr">
         <is>
-          <t>[R22→主证据矩阵#74] 天融信CHM:账号管理[topic53]+Local服务器[toc462834527]+短信[topic68]；PA:webhelp p839/p741/admin p236-240</t>
+          <t>[R22→M#74] ; TS:账号管理[e:topic53] + Local服务器[e:toc462834527] + 短信[e:topic68] ; PA-WEBHELP:[p:839][p:741] ; PA-ADMIN:[p:236-240]</t>
         </is>
       </c>
       <c r="N25" s="5" t="inlineStr">
@@ -2950,7 +2086,7 @@
       </c>
       <c r="M26" s="4" t="inlineStr">
         <is>
-          <t>[R23→主证据矩阵#5] 天融信CHM:配置访问控制策略；PA:Datasheet 规格表</t>
+          <t>[R23→M#5] ; TS:配置访问控制策略 ; PA-DS:规格表</t>
         </is>
       </c>
       <c r="N26" s="4" t="inlineStr">
@@ -3022,7 +2158,7 @@
       </c>
       <c r="M27" s="5" t="inlineStr">
         <is>
-          <t>[R24→主证据矩阵#92] 天融信CHM:固件维护[topic83]+引擎管理[topic84]+规则库升级[toc462834565]；PA:webhelp p846-847/p1091，admin p33</t>
+          <t>[R24→M#92] ; TS:固件维护[e:topic83] + 引擎管理[e:topic84] + 规则库升级[e:toc462834565] ; PA-WEBHELP:[p:846-847][p:1091] ; PA-ADMIN:[p:33]</t>
         </is>
       </c>
       <c r="N27" s="5" t="inlineStr">
@@ -3079,7 +2215,7 @@
       </c>
       <c r="M28" s="4" t="inlineStr">
         <is>
-          <t>[R25→主证据矩阵#135] 天融信CHM:登录安全策略[ref465087238]（仅账户级）；PA:webhelp p40，admin p100-101</t>
+          <t>[R25→M#135] ; TS:登录安全策略[e:ref465087238] ; PA-WEBHELP:[p:40] ; PA-ADMIN:[p:100-101] ; NOTE:仅账户级</t>
         </is>
       </c>
       <c r="N28" s="4" t="inlineStr">
@@ -3151,7 +2287,7 @@
       </c>
       <c r="M29" s="5" t="inlineStr">
         <is>
-          <t>[R26→主证据矩阵#10] 天融信CHM:策略路由[toc490041605]+路由[ref487714854]；PA:webhelp p156 PBF</t>
+          <t>[R26→M#10] ; TS:策略路由[e:toc490041605] + 路由[e:ref487714854] ; PA-WEBHELP:[p:156] ; PA-NOTE:PBF</t>
         </is>
       </c>
       <c r="N29" s="5" t="inlineStr">
@@ -3207,7 +2343,7 @@
       </c>
       <c r="M30" s="4" t="inlineStr">
         <is>
-          <t>[R27→主证据矩阵#10] 天融信CHM:策略路由[toc490041605]+路由[ref487714854]；PA:webhelp p156 PBF</t>
+          <t>[R27→M#10] ; TS:策略路由[e:toc490041605] + 路由[e:ref487714854] ; PA-WEBHELP:[p:156] ; PA-NOTE:PBF</t>
         </is>
       </c>
       <c r="N30" s="4" t="inlineStr">
@@ -3280,7 +2416,7 @@
       </c>
       <c r="M31" s="5" t="inlineStr">
         <is>
-          <t>[R28→主证据矩阵#90] 天融信CHM:配置维护[toc462834560]+管理用户[ref467487317]+CA管理[ca3]；PA:webhelp p653，admin p106-107/p1049</t>
+          <t>[R28→M#90] ; TS:配置维护[e:toc462834560] + 管理用户[e:ref467487317] + CA管理[e:ca3] ; PA-WEBHELP:[p:653] ; PA-ADMIN:[p:106-107][p:1049]</t>
         </is>
       </c>
       <c r="N31" s="5" t="inlineStr">
@@ -3352,7 +2488,7 @@
       </c>
       <c r="M32" s="4" t="inlineStr">
         <is>
-          <t>[R29→主证据矩阵#90] 天融信CHM:配置维护[toc462834560]+管理用户[ref467487317]+CA管理[ca3]；PA:webhelp p653，admin p106-107/p1049</t>
+          <t>[R29→M#90] ; TS:配置维护[e:toc462834560] + 管理用户[e:ref467487317] + CA管理[e:ca3] ; PA-WEBHELP:[p:653] ; PA-ADMIN:[p:106-107][p:1049]</t>
         </is>
       </c>
       <c r="N32" s="4" t="inlineStr">
@@ -3424,7 +2560,7 @@
       </c>
       <c r="M33" s="5" t="inlineStr">
         <is>
-          <t>[R30→主证据矩阵#90] 天融信CHM:配置维护[toc462834560]+管理用户[ref467487317]+CA管理[ca3]；PA:webhelp p653，admin p106-107/p1049</t>
+          <t>[R30→M#90] ; TS:配置维护[e:toc462834560] + 管理用户[e:ref467487317] + CA管理[e:ca3] ; PA-WEBHELP:[p:653] ; PA-ADMIN:[p:106-107][p:1049]</t>
         </is>
       </c>
       <c r="N33" s="5" t="inlineStr">
@@ -3496,7 +2632,7 @@
       </c>
       <c r="M34" s="4" t="inlineStr">
         <is>
-          <t>[R31→主证据矩阵#33] 天融信CHM:配置流量策略[toc399440500]；PA:webhelp p609/admin p1125</t>
+          <t>[R31→M#33] ; TS:配置流量策略[e:toc399440500] ; PA-WEBHELP:[p:609] ; PA-ADMIN:[p:1125]</t>
         </is>
       </c>
       <c r="N34" s="4" t="inlineStr">
@@ -3552,7 +2688,7 @@
       </c>
       <c r="M35" s="5" t="inlineStr">
         <is>
-          <t>[R32→主证据矩阵#33] 天融信CHM:配置流量策略[toc399440500]；PA:webhelp p609/admin p1125</t>
+          <t>[R32→M#33] ; TS:配置流量策略[e:toc399440500] ; PA-WEBHELP:[p:609] ; PA-ADMIN:[p:1125]</t>
         </is>
       </c>
       <c r="N35" s="5" t="inlineStr">
@@ -3620,7 +2756,7 @@
       </c>
       <c r="M36" s="4" t="inlineStr">
         <is>
-          <t>[R33→主证据矩阵#23] 天融信CHM:IPv4组播[ipv4.html]；PA:webhelp p469-472 多播</t>
+          <t>[R33→M#23] ; TS:IPv4组播[e:ipv4] ; PA-WEBHELP:[p:469-472] ; PA-NOTE:多播</t>
         </is>
       </c>
       <c r="N36" s="4" t="inlineStr">
@@ -3676,7 +2812,7 @@
       </c>
       <c r="M37" s="5" t="inlineStr">
         <is>
-          <t>[R34→主证据矩阵#23] 天融信CHM:IPv4组播[ipv4.html]；PA:webhelp p469-472 多播</t>
+          <t>[R34→M#23] ; TS:IPv4组播[e:ipv4] ; PA-WEBHELP:[p:469-472] ; PA-NOTE:多播</t>
         </is>
       </c>
       <c r="N37" s="5" t="inlineStr">
@@ -3732,7 +2868,7 @@
       </c>
       <c r="M38" s="4" t="inlineStr">
         <is>
-          <t>[R35→主证据矩阵#23] 天融信CHM:IPv4组播[ipv4.html]；PA:webhelp p469-472 多播</t>
+          <t>[R35→M#23] ; TS:IPv4组播[e:ipv4] ; PA-WEBHELP:[p:469-472] ; PA-NOTE:多播</t>
         </is>
       </c>
       <c r="N38" s="4" t="inlineStr">
@@ -3788,7 +2924,7 @@
       </c>
       <c r="M39" s="5" t="inlineStr">
         <is>
-          <t>[R36→主证据矩阵#23] 天融信CHM:IPv4组播[ipv4.html]；PA:webhelp p469-472 多播</t>
+          <t>[R36→M#23] ; TS:IPv4组播[e:ipv4] ; PA-WEBHELP:[p:469-472] ; PA-NOTE:多播</t>
         </is>
       </c>
       <c r="N39" s="5" t="inlineStr">
@@ -3856,7 +2992,7 @@
       </c>
       <c r="M40" s="4" t="inlineStr">
         <is>
-          <t>[R37→主证据矩阵#2] 天融信CHM:应用[toc448912175]+预定义应用[topic194]；PA:admin p920-940 App-ID</t>
+          <t>[R37→M#2] ; TS:应用[e:toc448912175] + 预定义应用[e:topic194] ; PA-ADMIN:[p:920-940] ; PA-NOTE:App-ID</t>
         </is>
       </c>
       <c r="N40" s="4" t="inlineStr">
@@ -3916,7 +3052,7 @@
       </c>
       <c r="M41" s="5" t="inlineStr">
         <is>
-          <t>[R38→主证据矩阵#39] 天融信CHM:入侵防御[topic10/200-202]+升级中心[topic61]；PA:Web帮助&gt;安全配置文件&gt;Vulnerability/Anti-Spyware+Device&gt;Dynamic Updates</t>
+          <t>[R38→M#39] ; TS:入侵防御[e:topic10] + 入侵防御[p:200-202] + 升级中心[e:topic61] ; PA-NOTE:Web帮助&gt;安全配置文件&gt;Vulnerability/Anti-Spyware+Device&gt;Dynamic Updates</t>
         </is>
       </c>
       <c r="N41" s="5" t="inlineStr">
@@ -3988,7 +3124,7 @@
       </c>
       <c r="M42" s="4" t="inlineStr">
         <is>
-          <t>[R39→主证据矩阵#57] 天融信CHM:URL分类[toc448912180]+预定义分类[topic191]；PA:webhelp p273-275/admin p73</t>
+          <t>[R39→M#57] ; TS:URL分类[e:toc448912180] + 预定义分类[e:topic191] ; PA-WEBHELP:[p:273-275] ; PA-ADMIN:[p:73]</t>
         </is>
       </c>
       <c r="N42" s="4" t="inlineStr">
@@ -4060,7 +3196,7 @@
       </c>
       <c r="M43" s="5" t="inlineStr">
         <is>
-          <t>[R40→主证据矩阵#53] 天融信CHM:WAF[anquancelue_waf]+爬虫[topic220]+登录页面[topic222]；PA:webhelp p270（否定证据：中文手册无WAF专章）</t>
+          <t>[R40→M#53] ; TS:WAF[e:anquancelue_waf] + 爬虫[e:topic220] + 登录页面[e:topic222] ; PA-WEBHELP:[p:270] ; NOTE:否定证据：中文手册无WAF专章</t>
         </is>
       </c>
       <c r="N43" s="5" t="inlineStr">
@@ -4116,7 +3252,7 @@
       </c>
       <c r="M44" s="4" t="inlineStr">
         <is>
-          <t>[R41→主证据矩阵#53] 天融信CHM:WAF[anquancelue_waf]+爬虫[topic220]+登录页面[topic222]；PA:webhelp p270（否定证据：中文手册无WAF专章）</t>
+          <t>[R41→M#53] ; TS:WAF[e:anquancelue_waf] + 爬虫[e:topic220] + 登录页面[e:topic222] ; PA-WEBHELP:[p:270] ; NOTE:否定证据：中文手册无WAF专章</t>
         </is>
       </c>
       <c r="N44" s="4" t="inlineStr">
@@ -4184,7 +3320,7 @@
       </c>
       <c r="M45" s="5" t="inlineStr">
         <is>
-          <t>[R42→主证据矩阵#46] 天融信CHM:APT联动[apt]+MD5查询[md5]+云安全中心[topic52]；PA:webhelp p283/admin p67-68</t>
+          <t>[R42→M#46] ; TS:APT联动[e:apt] + MD5查询[e:md5] + 云安全中心[e:topic52] ; PA-WEBHELP:[p:283] ; PA-ADMIN:[p:67-68]</t>
         </is>
       </c>
       <c r="N45" s="5" t="inlineStr">
@@ -4256,7 +3392,7 @@
       </c>
       <c r="M46" s="4" t="inlineStr">
         <is>
-          <t>[R43→主证据矩阵#80] 天融信CHM:登录系统[ngfw2]+通过浏览器登录[topic142]+熟悉WEB管理界面[toc490041566]；PA:webhelp p21/p26/p42，admin p89</t>
+          <t>[R43→M#80] ; TS:登录系统[e:ngfw2] + 通过浏览器登录[e:topic142] + 熟悉WEB管理界面[e:toc490041566] ; PA-WEBHELP:[p:21][p:26][p:42] ; PA-ADMIN:[p:89]</t>
         </is>
       </c>
       <c r="N46" s="4" t="inlineStr">
@@ -4324,7 +3460,7 @@
       </c>
       <c r="M47" s="5" t="inlineStr">
         <is>
-          <t>[R44→主证据矩阵#24] 天融信CHM:应用[toc448912175]；PA:admin p889-940 App-ID</t>
+          <t>[R44→M#24] ; TS:应用[e:toc448912175] ; PA-ADMIN:[p:889-940] ; PA-NOTE:App-ID</t>
         </is>
       </c>
       <c r="N47" s="5" t="inlineStr">
@@ -4380,7 +3516,7 @@
       </c>
       <c r="M48" s="4" t="inlineStr">
         <is>
-          <t>[R45→主证据矩阵#80] 天融信CHM:登录系统[ngfw2]+通过浏览器登录[topic142]+熟悉WEB管理界面[toc490041566]；PA:webhelp p21/p26/p42，admin p89</t>
+          <t>[R45→M#80] ; TS:登录系统[e:ngfw2] + 通过浏览器登录[e:topic142] + 熟悉WEB管理界面[e:toc490041566] ; PA-WEBHELP:[p:21][p:26][p:42] ; PA-ADMIN:[p:89]</t>
         </is>
       </c>
       <c r="N48" s="4" t="inlineStr">
@@ -4444,7 +3580,7 @@
       </c>
       <c r="M49" s="5" t="inlineStr">
         <is>
-          <t>[R46→主证据矩阵#84] 天融信CHM:日志配置[toc490041759]+日志服务器配置[ref465084227]+日志存储管理[topic212]；PA:webhelp p305/p808/p817/p721，admin p579/p589</t>
+          <t>[R46→M#84] ; TS:日志配置[e:toc490041759] + 日志服务器配置[e:ref465084227] + 日志存储管理[e:topic212] ; PA-WEBHELP:[p:305][p:808][p:817][p:721] ; PA-ADMIN:[p:579][p:589]</t>
         </is>
       </c>
       <c r="N49" s="5" t="inlineStr">
@@ -4508,7 +3644,7 @@
       </c>
       <c r="M50" s="4" t="inlineStr">
         <is>
-          <t>[R47→主证据矩阵#86] 天融信CHM:报表配置[topic21]+模板管理[topic23]+攻击者[topic55]；PA:webhelp p107/p109，admin p553-570</t>
+          <t>[R47→M#86] ; TS:报表配置[e:topic21] + 模板管理[e:topic23] + 攻击者[e:topic55] ; PA-WEBHELP:[p:107][p:109] ; PA-ADMIN:[p:553-570]</t>
         </is>
       </c>
       <c r="N50" s="4" t="inlineStr">
@@ -4577,7 +3713,7 @@
       </c>
       <c r="M51" s="5" t="inlineStr">
         <is>
-          <t>[R48→主证据矩阵#95] 天融信CHM:系统组成[topic32]（型号信息缺失）；PA:webhelp p526/p1018，admin p379/p1312</t>
+          <t>[R48→M#95] ; TS:系统组成[e:topic32] ; PA-WEBHELP:[p:526][p:1018] ; PA-ADMIN:[p:379][p:1312] ; NOTE:型号信息缺失</t>
         </is>
       </c>
       <c r="N51" s="5" t="inlineStr">
@@ -4645,7 +3781,7 @@
       </c>
       <c r="M52" s="4" t="inlineStr">
         <is>
-          <t>[R49→主证据矩阵#97] 天融信CHM:系统组成[topic32]；PA:admin p329/p477/p1329（插槽表述仅限PA-7000）</t>
+          <t>[R49→M#97] ; TS:系统组成[e:topic32] ; PA-ADMIN:[p:329][p:477][p:1329] ; NOTE:插槽表述仅限PA-7000</t>
         </is>
       </c>
       <c r="N52" s="4" t="inlineStr">
@@ -4713,7 +3849,7 @@
       </c>
       <c r="M53" s="5" t="inlineStr">
         <is>
-          <t>[R50→主证据矩阵#97] 天融信CHM:系统组成[topic32]；PA:admin p329/p477/p1329（插槽表述仅限PA-7000）</t>
+          <t>[R50→M#97] ; TS:系统组成[e:topic32] ; PA-ADMIN:[p:329][p:477][p:1329] ; NOTE:插槽表述仅限PA-7000</t>
         </is>
       </c>
       <c r="N53" s="5" t="inlineStr">
@@ -4786,7 +3922,7 @@
       </c>
       <c r="M54" s="4" t="inlineStr">
         <is>
-          <t>[R51→主证据矩阵#97] 天融信CHM:系统组成[topic32]；PA:admin p329/p477/p1329（插槽表述仅限PA-7000）</t>
+          <t>[R51→M#97] ; TS:系统组成[e:topic32] ; PA-ADMIN:[p:329][p:477][p:1329] ; NOTE:插槽表述仅限PA-7000</t>
         </is>
       </c>
       <c r="N54" s="4" t="inlineStr">
@@ -4854,7 +3990,7 @@
       </c>
       <c r="M55" s="5" t="inlineStr">
         <is>
-          <t>[R52→主证据矩阵#87] 天融信CHM:高可用性[toc462834583]+配置[topic15/136/140/141]；PA:admin p377-399/p411，webhelp p706-717</t>
+          <t>[R52→M#87] ; TS:高可用性[e:toc462834583] + 配置[e:topic15] + 配置[p:136] + 配置[p:140] + 配置[p:141] ; PA-WEBHELP:[p:706-717] ; PA-ADMIN:[p:377-399][p:411]</t>
         </is>
       </c>
       <c r="N55" s="5" t="inlineStr">
@@ -4926,7 +4062,7 @@
       </c>
       <c r="M56" s="4" t="inlineStr">
         <is>
-          <t>[R53→主证据矩阵#19] 天融信CHM:虚拟系统[xunixitong/topic128]；PA:webhelp p780-781/admin p1312</t>
+          <t>[R53→M#19] ; TS:虚拟系统[e:xunixitong] + 虚拟系统[e:topic128] ; PA-WEBHELP:[p:780-781] ; PA-ADMIN:[p:1312]</t>
         </is>
       </c>
       <c r="N56" s="4" t="inlineStr">
@@ -4994,7 +4130,7 @@
       </c>
       <c r="M57" s="5" t="inlineStr">
         <is>
-          <t>[R54→主证据矩阵#5] 天融信CHM:配置访问控制策略；PA:Datasheet 规格表</t>
+          <t>[R54→M#5] ; TS:配置访问控制策略 ; PA-DS:规格表</t>
         </is>
       </c>
       <c r="N57" s="5" t="inlineStr">
@@ -5068,7 +4204,7 @@
       </c>
       <c r="M58" s="4" t="inlineStr">
         <is>
-          <t>[R55→主证据矩阵#96] 天融信CHM:系统组成[topic32]+配置接口高级信息[ref487722465]；PA:webhelp p332-341/p428，admin p477</t>
+          <t>[R55→M#96] ; TS:系统组成[e:topic32] + 配置接口高级信息[e:ref487722465] ; PA-WEBHELP:[p:332-341][p:428] ; PA-ADMIN:[p:477]</t>
         </is>
       </c>
       <c r="N58" s="4" t="inlineStr">
@@ -5140,7 +4276,7 @@
       </c>
       <c r="M59" s="5" t="inlineStr">
         <is>
-          <t>[R56→主证据矩阵#96] 天融信CHM:系统组成[topic32]+配置接口高级信息[ref487722465]；PA:webhelp p332-341/p428，admin p477</t>
+          <t>[R56→M#96] ; TS:系统组成[e:topic32] + 配置接口高级信息[e:ref487722465] ; PA-WEBHELP:[p:332-341][p:428] ; PA-ADMIN:[p:477]</t>
         </is>
       </c>
       <c r="N59" s="5" t="inlineStr">
@@ -5212,7 +4348,7 @@
       </c>
       <c r="M60" s="4" t="inlineStr">
         <is>
-          <t>[R57→主证据矩阵#77] 天融信CHM:静态隧道[topic4]+链路备份[toc462834587]+高可用[toc462834581]；PA:webhelp p439/admin p1168</t>
+          <t>[R57→M#77] ; TS:静态隧道[e:topic4] + 链路备份[e:toc462834587] + 高可用[e:toc462834581] ; PA-WEBHELP:[p:439] ; PA-ADMIN:[p:1168]</t>
         </is>
       </c>
       <c r="N60" s="4" t="inlineStr">
@@ -5280,7 +4416,7 @@
       </c>
       <c r="M61" s="5" t="inlineStr">
         <is>
-          <t>[R58→主证据矩阵#124] PA:webhelp p312 解密镜像接口+admin p1114</t>
+          <t>[R58→M#124] ; PA-WEBHELP:[p:312] ; PA-ADMIN:[p:1114] ; PA-NOTE:解密镜像接口</t>
         </is>
       </c>
       <c r="N61" s="5" t="inlineStr">
@@ -5295,12 +4431,11 @@
     <mergeCell ref="A1:N1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
@@ -13174,7 +12309,7 @@
       </c>
       <c r="F135" s="9" t="inlineStr">
         <is>
-          <t>SSL卸载策略（解密后送安全引擎检测）；“解密流量镜像到外部接口”专用功能未见手册说明——待验证（R58）</t>
+          <t>SSL卸载策略（解密后送安全引擎检测）；"解密流量镜像到外部接口"专用功能未见手册说明（已核实，R58）</t>
         </is>
       </c>
       <c r="G135" s="12" t="inlineStr">
@@ -13189,7 +12324,7 @@
       </c>
       <c r="I135" s="9" t="inlineStr">
         <is>
-          <t>待验证</t>
+          <t>PA优势（天融信无解密流量镜像专用功能，仅SSL卸载+WAF镜像联动）</t>
         </is>
       </c>
       <c r="J135" s="9" t="inlineStr">
@@ -14114,12 +13249,11 @@
     <mergeCell ref="A1:L1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
@@ -17591,12 +16725,11 @@
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
@@ -18642,12 +17775,11 @@
     <mergeCell ref="A1:J1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
@@ -18927,12 +18059,11 @@
     <mergeCell ref="A1:C1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
@@ -20817,6 +19948,5 @@
     <mergeCell ref="A1:F1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>